--- a/artfynd/A 69626-2021 artfynd.xlsx
+++ b/artfynd/A 69626-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69626-2021 artfynd.xlsx
+++ b/artfynd/A 69626-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3834,10 +3834,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109909861</v>
+        <v>109909849</v>
       </c>
       <c r="B29" t="n">
-        <v>89406</v>
+        <v>89388</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3850,21 +3850,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3874,10 +3874,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725255.4016472457</v>
+        <v>725305.5492305406</v>
       </c>
       <c r="R29" t="n">
-        <v>7119332.843257072</v>
+        <v>7119397.415435524</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3951,10 +3951,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109909849</v>
+        <v>109909848</v>
       </c>
       <c r="B30" t="n">
-        <v>89388</v>
+        <v>81236</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3967,21 +3967,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725305.5492305406</v>
+        <v>725277.4779498863</v>
       </c>
       <c r="R30" t="n">
-        <v>7119397.415435524</v>
+        <v>7119403.258429548</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4068,10 +4068,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109909848</v>
+        <v>109909853</v>
       </c>
       <c r="B31" t="n">
-        <v>81236</v>
+        <v>89410</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4084,21 +4084,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725277.4779498863</v>
+        <v>725352.4537208345</v>
       </c>
       <c r="R31" t="n">
-        <v>7119403.258429548</v>
+        <v>7119392.068862542</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4185,10 +4185,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109909853</v>
+        <v>109909858</v>
       </c>
       <c r="B32" t="n">
-        <v>89410</v>
+        <v>89832</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4197,25 +4197,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>725352.4537208345</v>
+        <v>725153.8689862577</v>
       </c>
       <c r="R32" t="n">
-        <v>7119392.068862542</v>
+        <v>7119431.505153495</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4302,10 +4302,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109909858</v>
+        <v>109909852</v>
       </c>
       <c r="B33" t="n">
-        <v>89832</v>
+        <v>89392</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4314,25 +4314,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>725153.8689862577</v>
+        <v>725316.9520452726</v>
       </c>
       <c r="R33" t="n">
-        <v>7119431.505153495</v>
+        <v>7119427.609448032</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109909852</v>
+        <v>112610245</v>
       </c>
       <c r="B34" t="n">
-        <v>89392</v>
+        <v>89785</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4435,21 +4435,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>725316.9520452726</v>
+        <v>725259</v>
       </c>
       <c r="R34" t="n">
-        <v>7119427.609448032</v>
+        <v>7119348</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4492,19 +4492,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4536,10 +4526,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112606209</v>
+        <v>112610258</v>
       </c>
       <c r="B35" t="n">
-        <v>90052</v>
+        <v>89789</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4552,21 +4542,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4576,10 +4566,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>725156</v>
+        <v>725159</v>
       </c>
       <c r="R35" t="n">
-        <v>7119429</v>
+        <v>7119164</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4643,10 +4633,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112606227</v>
+        <v>112610235</v>
       </c>
       <c r="B36" t="n">
-        <v>77856</v>
+        <v>89767</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4659,21 +4649,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4683,10 +4673,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>725116</v>
+        <v>725277</v>
       </c>
       <c r="R36" t="n">
-        <v>7119246</v>
+        <v>7119403</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4750,10 +4740,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112606215</v>
+        <v>112610243</v>
       </c>
       <c r="B37" t="n">
-        <v>77856</v>
+        <v>90052</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4766,21 +4756,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4790,10 +4780,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>725210</v>
+        <v>725154</v>
       </c>
       <c r="R37" t="n">
-        <v>7119337</v>
+        <v>7119432</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4857,10 +4847,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112606204</v>
+        <v>112610237</v>
       </c>
       <c r="B38" t="n">
-        <v>89789</v>
+        <v>89771</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4873,21 +4863,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4897,10 +4887,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>725318</v>
+        <v>725309</v>
       </c>
       <c r="R38" t="n">
-        <v>7119429</v>
+        <v>7119409</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4964,10 +4954,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112610245</v>
+        <v>112610244</v>
       </c>
       <c r="B39" t="n">
-        <v>89785</v>
+        <v>90211</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4976,25 +4966,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5004,10 +4994,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>725259</v>
+        <v>725213</v>
       </c>
       <c r="R39" t="n">
-        <v>7119348</v>
+        <v>7119404</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5071,10 +5061,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112610246</v>
+        <v>112610239</v>
       </c>
       <c r="B40" t="n">
-        <v>89785</v>
+        <v>90211</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5083,25 +5073,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5111,10 +5101,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>725255</v>
+        <v>725352</v>
       </c>
       <c r="R40" t="n">
-        <v>7119333</v>
+        <v>7119392</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5178,10 +5168,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112606206</v>
+        <v>112610238</v>
       </c>
       <c r="B41" t="n">
-        <v>90211</v>
+        <v>89789</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5190,25 +5180,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5218,10 +5208,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>725235</v>
+        <v>725317</v>
       </c>
       <c r="R41" t="n">
-        <v>7119390</v>
+        <v>7119428</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5282,2788 +5272,6 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>112606207</v>
-      </c>
-      <c r="B42" t="n">
-        <v>90211</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>725227</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7119439</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>112610242</v>
-      </c>
-      <c r="B43" t="n">
-        <v>90211</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>725149</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7119429</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>112606203</v>
-      </c>
-      <c r="B44" t="n">
-        <v>89771</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>725311</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7119411</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>112606200</v>
-      </c>
-      <c r="B45" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>725260</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7119369</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>112610240</v>
-      </c>
-      <c r="B46" t="n">
-        <v>90211</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>725233</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7119393</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>112606210</v>
-      </c>
-      <c r="B47" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>725190</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7119399</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>112610258</v>
-      </c>
-      <c r="B48" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>725159</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7119164</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>112606213</v>
-      </c>
-      <c r="B49" t="n">
-        <v>89785</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>725255</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7119334</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>112606211</v>
-      </c>
-      <c r="B50" t="n">
-        <v>90211</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>725213</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7119402</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>112610247</v>
-      </c>
-      <c r="B51" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>725211</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7119338</v>
-      </c>
-      <c r="S51" t="n">
-        <v>10</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>112606201</v>
-      </c>
-      <c r="B52" t="n">
-        <v>89767</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>725277</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7119398</v>
-      </c>
-      <c r="S52" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>112610235</v>
-      </c>
-      <c r="B53" t="n">
-        <v>89767</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>725277</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7119403</v>
-      </c>
-      <c r="S53" t="n">
-        <v>10</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>112610243</v>
-      </c>
-      <c r="B54" t="n">
-        <v>90052</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>658</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>725154</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7119432</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>112606214</v>
-      </c>
-      <c r="B55" t="n">
-        <v>55834</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>725249</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7119327</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>112610237</v>
-      </c>
-      <c r="B56" t="n">
-        <v>89771</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>725309</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7119409</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>112610241</v>
-      </c>
-      <c r="B57" t="n">
-        <v>90211</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>725226</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7119442</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>112606212</v>
-      </c>
-      <c r="B58" t="n">
-        <v>89785</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>725259</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7119350</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>112610244</v>
-      </c>
-      <c r="B59" t="n">
-        <v>90211</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>725213</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7119404</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>112606225</v>
-      </c>
-      <c r="B60" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>725153</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7119112</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>112606202</v>
-      </c>
-      <c r="B61" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>725306</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7119397</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>112610239</v>
-      </c>
-      <c r="B62" t="n">
-        <v>90211</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>725352</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7119392</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>112606208</v>
-      </c>
-      <c r="B63" t="n">
-        <v>90211</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>725147</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7119435</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>112606222</v>
-      </c>
-      <c r="B64" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>725159</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7119165</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>112606226</v>
-      </c>
-      <c r="B65" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>725119</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7119249</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>112610238</v>
-      </c>
-      <c r="B66" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>725317</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7119428</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>112606216</v>
-      </c>
-      <c r="B67" t="n">
-        <v>90211</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Hälsingfors, Vb</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>725206</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7119306</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Vindeln</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Degerfors</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 69626-2021 artfynd.xlsx
+++ b/artfynd/A 69626-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104159485</v>
+        <v>112606209</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725210.3061156402</v>
+        <v>725156</v>
       </c>
       <c r="R2" t="n">
-        <v>7119337.446749515</v>
+        <v>7119429</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104159482</v>
+        <v>112610243</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725258.9962534721</v>
+        <v>725154</v>
       </c>
       <c r="R3" t="n">
-        <v>7119349.759125493</v>
+        <v>7119431</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,24 +845,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104159470</v>
+        <v>112606201</v>
       </c>
       <c r="B4" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725277.4226376007</v>
+        <v>725277</v>
       </c>
       <c r="R4" t="n">
-        <v>7119397.995344399</v>
+        <v>7119398</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,24 +947,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104159479</v>
+        <v>112610235</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725190.4558165995</v>
+        <v>725277</v>
       </c>
       <c r="R5" t="n">
-        <v>7119399.109885342</v>
+        <v>7119403</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,24 +1049,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104159499</v>
+        <v>112606203</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725119.3370935626</v>
+        <v>725311</v>
       </c>
       <c r="R6" t="n">
-        <v>7119248.865788803</v>
+        <v>7119410</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,24 +1151,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104159483</v>
+        <v>112606224</v>
       </c>
       <c r="B7" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725255.3381226237</v>
+        <v>725164</v>
       </c>
       <c r="R7" t="n">
-        <v>7119333.715155718</v>
+        <v>7119140</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,24 +1253,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104159493</v>
+        <v>112610237</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725159.2035114354</v>
+        <v>725309</v>
       </c>
       <c r="R8" t="n">
-        <v>7119165.427881023</v>
+        <v>7119408</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,24 +1355,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104159469</v>
+        <v>112610261</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725259.8129727425</v>
+        <v>725166</v>
       </c>
       <c r="R9" t="n">
-        <v>7119368.663808436</v>
+        <v>7119137</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,24 +1457,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,37 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104159484</v>
+        <v>112606212</v>
       </c>
       <c r="B10" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725249.2669120079</v>
+        <v>725259</v>
       </c>
       <c r="R10" t="n">
-        <v>7119326.698869988</v>
+        <v>7119350</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,24 +1559,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,37 +1593,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104159471</v>
+        <v>112606213</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1768,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725305.5492305406</v>
+        <v>725255</v>
       </c>
       <c r="R11" t="n">
-        <v>7119397.415435524</v>
+        <v>7119334</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,24 +1661,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,15 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104159480</v>
+        <v>112610245</v>
       </c>
       <c r="B12" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,21 +1706,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725213.4950083354</v>
+        <v>725259</v>
       </c>
       <c r="R12" t="n">
-        <v>7119402.102876347</v>
+        <v>7119348</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,24 +1763,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1962,15 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104159477</v>
+        <v>112610246</v>
       </c>
       <c r="B13" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1978,21 +1808,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2002,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725147.0675870196</v>
+        <v>725255</v>
       </c>
       <c r="R13" t="n">
-        <v>7119434.515806356</v>
+        <v>7119333</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2035,24 +1865,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2079,15 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104159472</v>
+        <v>112606205</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,21 +1910,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2119,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725311.175386166</v>
+        <v>725354</v>
       </c>
       <c r="R14" t="n">
-        <v>7119410.534842022</v>
+        <v>7119385</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,24 +1967,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,19 +2001,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104159476</v>
+        <v>112606206</v>
       </c>
       <c r="B15" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2221,12 +2021,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2236,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725227.0094958941</v>
+        <v>725235</v>
       </c>
       <c r="R15" t="n">
-        <v>7119439.462179341</v>
+        <v>7119389</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,24 +2069,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2313,19 +2103,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104159486</v>
+        <v>112606207</v>
       </c>
       <c r="B16" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2338,12 +2123,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2353,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725206.4496224059</v>
+        <v>725227</v>
       </c>
       <c r="R16" t="n">
-        <v>7119306.049090588</v>
+        <v>7119440</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2386,24 +2171,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2430,15 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104159473</v>
+        <v>112606208</v>
       </c>
       <c r="B17" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2446,21 +2216,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2470,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725318.1979893692</v>
+        <v>725147</v>
       </c>
       <c r="R17" t="n">
-        <v>7119428.576756559</v>
+        <v>7119434</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2503,24 +2273,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2547,15 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104159500</v>
+        <v>112606211</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,21 +2318,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2587,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725116.4719055519</v>
+        <v>725213</v>
       </c>
       <c r="R18" t="n">
-        <v>7119246.027538204</v>
+        <v>7119402</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,24 +2375,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2664,15 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104159478</v>
+        <v>112606216</v>
       </c>
       <c r="B19" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2680,21 +2420,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2704,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725156.2102024588</v>
+        <v>725207</v>
       </c>
       <c r="R19" t="n">
-        <v>7119429.484422152</v>
+        <v>7119306</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2737,24 +2477,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2781,19 +2511,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104159475</v>
+        <v>112606217</v>
       </c>
       <c r="B20" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2806,12 +2531,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2821,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>725235.4632629482</v>
+        <v>725206</v>
       </c>
       <c r="R20" t="n">
-        <v>7119389.679127658</v>
+        <v>7119294</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2854,24 +2579,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2898,15 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104159496</v>
+        <v>112606218</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2914,21 +2624,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2938,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>725153.0364173674</v>
+        <v>725165</v>
       </c>
       <c r="R21" t="n">
-        <v>7119111.507610803</v>
+        <v>7119221</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2971,24 +2681,14 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3015,19 +2715,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109909857</v>
+        <v>112606223</v>
       </c>
       <c r="B22" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3040,12 +2735,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3055,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>725149.1945345873</v>
+        <v>725163</v>
       </c>
       <c r="R22" t="n">
-        <v>7119429.411736825</v>
+        <v>7119142</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3088,19 +2783,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3132,19 +2817,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109909855</v>
+        <v>112610239</v>
       </c>
       <c r="B23" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3157,12 +2837,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3172,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>725225.9141993497</v>
+        <v>725352</v>
       </c>
       <c r="R23" t="n">
-        <v>7119442.45011956</v>
+        <v>7119392</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3205,19 +2885,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3249,15 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109909862</v>
+        <v>112610240</v>
       </c>
       <c r="B24" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,21 +2930,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3289,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>725211.1156197079</v>
+        <v>725234</v>
       </c>
       <c r="R24" t="n">
-        <v>7119338.382240199</v>
+        <v>7119393</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3322,19 +2987,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3366,19 +3021,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109909860</v>
+        <v>112610241</v>
       </c>
       <c r="B25" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3391,12 +3041,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3406,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725259.1233049497</v>
+        <v>725226</v>
       </c>
       <c r="R25" t="n">
-        <v>7119348.015336953</v>
+        <v>7119443</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3439,19 +3089,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3483,15 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109909859</v>
+        <v>112610242</v>
       </c>
       <c r="B26" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3499,21 +3134,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3523,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725213.3362255218</v>
+        <v>725149</v>
       </c>
       <c r="R26" t="n">
-        <v>7119404.282573273</v>
+        <v>7119430</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3556,19 +3191,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3600,15 +3225,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109909850</v>
+        <v>112610244</v>
       </c>
       <c r="B27" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3616,21 +3236,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3640,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>725309.119976196</v>
+        <v>725214</v>
       </c>
       <c r="R27" t="n">
-        <v>7119408.632032176</v>
+        <v>7119404</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3673,19 +3293,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3717,19 +3327,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109909854</v>
+        <v>112610249</v>
       </c>
       <c r="B28" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3742,12 +3347,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3757,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>725233.4314253004</v>
+        <v>725209</v>
       </c>
       <c r="R28" t="n">
-        <v>7119393.475396252</v>
+        <v>7119301</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3790,19 +3395,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3834,15 +3429,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109909849</v>
+        <v>112610250</v>
       </c>
       <c r="B29" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3850,21 +3440,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3874,10 +3464,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725305.5492305406</v>
+        <v>725207</v>
       </c>
       <c r="R29" t="n">
-        <v>7119397.415435524</v>
+        <v>7119303</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3907,19 +3497,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3951,15 +3531,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109909848</v>
+        <v>112610251</v>
       </c>
       <c r="B30" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3967,21 +3542,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3991,10 +3566,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725277.4779498863</v>
+        <v>725164</v>
       </c>
       <c r="R30" t="n">
-        <v>7119403.258429548</v>
+        <v>7119227</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4024,19 +3599,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4068,15 +3633,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109909853</v>
+        <v>112610260</v>
       </c>
       <c r="B31" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4084,21 +3644,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4108,10 +3668,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725352.4537208345</v>
+        <v>725158</v>
       </c>
       <c r="R31" t="n">
-        <v>7119392.068862542</v>
+        <v>7119148</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4141,19 +3701,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4185,15 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109909858</v>
+        <v>112606202</v>
       </c>
       <c r="B32" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4201,21 +3746,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4225,10 +3770,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>725153.8689862577</v>
+        <v>725305</v>
       </c>
       <c r="R32" t="n">
-        <v>7119431.505153495</v>
+        <v>7119397</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4258,19 +3803,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4302,37 +3837,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109909852</v>
+        <v>112606210</v>
       </c>
       <c r="B33" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4342,10 +3872,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>725316.9520452726</v>
+        <v>725190</v>
       </c>
       <c r="R33" t="n">
-        <v>7119427.609448032</v>
+        <v>7119399</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4375,19 +3905,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4419,37 +3939,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112610245</v>
+        <v>112606215</v>
       </c>
       <c r="B34" t="n">
-        <v>89785</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4459,10 +3974,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>725259</v>
+        <v>725210</v>
       </c>
       <c r="R34" t="n">
-        <v>7119348</v>
+        <v>7119337</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4526,37 +4041,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112610258</v>
+        <v>112606220</v>
       </c>
       <c r="B35" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4566,10 +4076,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>725159</v>
+        <v>725174</v>
       </c>
       <c r="R35" t="n">
-        <v>7119164</v>
+        <v>7119205</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4633,37 +4143,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112610235</v>
+        <v>112606225</v>
       </c>
       <c r="B36" t="n">
-        <v>89767</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4673,10 +4178,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>725277</v>
+        <v>725153</v>
       </c>
       <c r="R36" t="n">
-        <v>7119403</v>
+        <v>7119112</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4740,37 +4245,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112610243</v>
+        <v>112606227</v>
       </c>
       <c r="B37" t="n">
-        <v>90052</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4780,10 +4280,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>725154</v>
+        <v>725116</v>
       </c>
       <c r="R37" t="n">
-        <v>7119432</v>
+        <v>7119246</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4847,37 +4347,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112610237</v>
+        <v>112610247</v>
       </c>
       <c r="B38" t="n">
-        <v>89771</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4887,10 +4382,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>725309</v>
+        <v>725211</v>
       </c>
       <c r="R38" t="n">
-        <v>7119409</v>
+        <v>7119338</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4954,37 +4449,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112610244</v>
+        <v>112606226</v>
       </c>
       <c r="B39" t="n">
-        <v>90211</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4994,10 +4484,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>725213</v>
+        <v>725119</v>
       </c>
       <c r="R39" t="n">
-        <v>7119404</v>
+        <v>7119249</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5061,37 +4551,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112610239</v>
+        <v>112606214</v>
       </c>
       <c r="B40" t="n">
-        <v>90211</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5101,10 +4586,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>725352</v>
+        <v>725249</v>
       </c>
       <c r="R40" t="n">
-        <v>7119392</v>
+        <v>7119327</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5168,15 +4653,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112610238</v>
+        <v>112606221</v>
       </c>
       <c r="B41" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5184,21 +4664,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5208,10 +4688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>725317</v>
+        <v>725165</v>
       </c>
       <c r="R41" t="n">
-        <v>7119428</v>
+        <v>7119179</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5272,6 +4752,108 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>112610257</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hälsingfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>725168</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7119180</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 69626-2021 artfynd.xlsx
+++ b/artfynd/A 69626-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606209</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610243</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606201</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610235</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606203</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606224</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610237</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610261</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606212</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606213</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610245</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610246</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606205</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606206</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606207</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606208</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606211</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606216</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2610,6 +2705,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606217</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606218</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2814,6 +2919,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606223</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610239</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3018,6 +3133,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610240</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3120,6 +3240,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610241</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3222,6 +3347,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610242</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3324,6 +3454,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610244</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3426,6 +3561,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610249</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3528,6 +3668,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610250</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3630,6 +3775,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610251</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3732,6 +3882,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610260</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3834,6 +3989,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606202</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3936,6 +4096,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606210</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4038,6 +4203,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606215</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4140,6 +4310,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606220</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4242,6 +4417,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606225</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4344,6 +4524,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606227</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4446,6 +4631,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610247</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4548,6 +4738,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606226</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4650,6 +4845,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606214</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4752,6 +4952,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606221</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4854,8 +5059,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610257</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>